--- a/templates/今日_Cafre_Peringatan_Penipuan/scripts.xlsx
+++ b/templates/今日_Cafre_Peringatan_Penipuan/scripts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,23 +446,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Nagpur Man Arrested in 3.81 Crore Fake Forex Scam</t>
+          <t>64 Crore AI Banking Scam Teen Arrested</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A fake forex trading scheme has led to a 3.81 crore rupee cyber fraud, and now, one key suspect has been arrested.
-Rajasthan Police arrested a Nagpur man accused of supplying bank accounts used by an interstate cyber fraud syndicate.
-According to investigators, a Jaipur-based doctor was lured through a Telegram group promising high forex trading returns.
-After showing fake profits, the scammers allegedly convinced the victim to invest 3.81 crore rupees.
-When he tried to withdraw the money, the group disappeared, chats were deleted, and all contact was cut off.
-Police are now tracing the wider network and following the money trail.
-Always verify trading platforms, avoid investment schemes shared through messaging apps, and remember, if returns seem too good to be true, they probably are.</t>
+          <t>An 18-year-old allegedly used AI to build fake banking apps that helped cybercriminals steal over 64 crore rupees across India. Here's what happened.
+Surat Police have arrested an 18-year-old accused of developing 121 fake Android APK apps that looked like genuine banking, payment, and government applications.
+According to investigators, the malware gave scammers remote access to victims' phones, allowing them to steal OTPs, banking passwords, and other sensitive information.
+The accused allegedly learned coding through YouTube and AI tools, then sold the malware to cybercrime gangs on a subscription model, charging 10,000 to 15,000 rupees per month.
+Police say the fake apps were linked to over 21,000 infected devices, more than 54,000 fraudulent transactions, and an estimated 64.38 crore rupees in losses.
+The investigation began after a Surat businessman lost 5 lakh rupees by installing a fake PNB One APK received on WhatsApp.
+Authorities have now seized the suspect's laptop and mobile phones, and the investigation is continuing to identify more victims and accomplices.
+Never install banking apps from WhatsApp links, SMS, or unknown websites.
+Always download apps only from the official Google Play Store or Apple App Store, and verify before entering your banking details.
+Stay alert. A single fake app can empty your bank account.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fake forex trading scam India Nagpur Rajasthan police Telegram cyber fraud arrest bank accounts</t>
+          <t>fake banking apps APK malware AI India Surat police teen arrested OTP fraud cybercrime remote access</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -473,38 +476,6 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>en</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ratu Investasi Bodong Bengkulu Kena Ciduk</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Selebgram terkenal, korban puluhan orang, kerugian mencapai enam miliar rupiah. Kasus investasi bodong kembali bikin heboh!
-Selebgram Bengkulu berinisial NC alias Yeyen atau Cik Oboy ditangkap polisi atas dugaan penipuan bermodus investasi bodong. Polisi menyebut penangkapan dilakukan setelah menemukan bukti yang cukup untuk proses penyidikan.
-Menurut kuasa hukum korban, sekitar enam puluh lima orang diduga menjadi korban dengan total kerugian mencapai enam miliar rupiah. Modusnya diduga menggunakan uang korban untuk membeli aset dengan nama pihak lain.
-Kasus ini jadi pengingat bahwa popularitas bukan berarti investasi tersebut aman. Banyak followers, gaya hidup mewah, atau janji keuntungan besar bukan bukti legalitas.
-Sebelum investasi, selalu cek izin, pahami risikonya, dan jangan mudah percaya hanya karena ditawarkan orang terkenal. Cek broker dan platform investasi sebelum dana kamu hilang.
-Temukan informasi dan laporkan pengalaman investasi mencurigakan lewat WikiFX.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>investasi bodong selebgram Bengkulu penipuan korban kerugian miliar polisi tangkap</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>PERINGATAN PENIPUAN</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>id</t>
         </is>
       </c>
     </row>
